--- a/research/traditional_assets/database/data/united_kingdom/united_kingdom_semiconductor_equip.xlsx
+++ b/research/traditional_assets/database/data/united_kingdom/united_kingdom_semiconductor_equip.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0277</v>
+        <v>-0.0327</v>
       </c>
       <c r="G2">
-        <v>0.1157706093189964</v>
+        <v>0.1351829988193624</v>
       </c>
       <c r="H2">
-        <v>0.03435739887352791</v>
+        <v>0.1351829988193624</v>
       </c>
       <c r="I2">
-        <v>-0.07731694828469021</v>
+        <v>-0.1463990554899646</v>
       </c>
       <c r="J2">
-        <v>-0.07731694828469021</v>
+        <v>-0.1463990554899646</v>
       </c>
       <c r="K2">
-        <v>-44.4</v>
+        <v>-111.3</v>
       </c>
       <c r="L2">
-        <v>-0.2273425499231951</v>
+        <v>-0.6570247933884297</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>18.7</v>
+        <v>15.6</v>
       </c>
       <c r="V2">
-        <v>0.03883696780893042</v>
+        <v>0.05198267244251915</v>
       </c>
       <c r="W2">
-        <v>-0.1256366723259762</v>
+        <v>-0.3748736948467498</v>
       </c>
       <c r="X2">
-        <v>0.1965032588824319</v>
+        <v>0.1661181589380553</v>
       </c>
       <c r="Y2">
-        <v>-0.3221399312084081</v>
+        <v>-0.5409918537848051</v>
       </c>
       <c r="Z2">
-        <v>0.4596375617792422</v>
+        <v>0.4574669187145557</v>
       </c>
       <c r="AA2">
-        <v>-0.03553777359378677</v>
+        <v>-0.06697272481771537</v>
       </c>
       <c r="AB2">
-        <v>0.1724582500740713</v>
+        <v>0.142196188216278</v>
       </c>
       <c r="AC2">
-        <v>-0.207996023667858</v>
+        <v>-0.2091689130339934</v>
       </c>
       <c r="AD2">
-        <v>92.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>92.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AG2">
-        <v>73.39999999999999</v>
+        <v>56.8</v>
       </c>
       <c r="AH2">
-        <v>0.1605648535564853</v>
+        <v>0.1943624161073826</v>
       </c>
       <c r="AI2">
-        <v>0.2367609254498715</v>
+        <v>0.24409979770735</v>
       </c>
       <c r="AJ2">
-        <v>0.1322760857812218</v>
+        <v>0.1591482207901373</v>
       </c>
       <c r="AK2">
-        <v>0.1982176613556576</v>
+        <v>0.202135231316726</v>
       </c>
       <c r="AL2">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="AM2">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="AN2">
-        <v>45.59405940594059</v>
+        <v>41.13636363636364</v>
       </c>
       <c r="AO2">
-        <v>-5.531135531135531</v>
+        <v>-6.231155778894473</v>
       </c>
       <c r="AP2">
-        <v>36.33663366336634</v>
+        <v>32.27272727272727</v>
       </c>
       <c r="AQ2">
-        <v>-5.531135531135531</v>
+        <v>-6.231155778894473</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0277</v>
+        <v>-0.0327</v>
       </c>
       <c r="G3">
-        <v>0.1157706093189964</v>
+        <v>0.1351829988193624</v>
       </c>
       <c r="H3">
-        <v>0.03435739887352791</v>
+        <v>0.1351829988193624</v>
       </c>
       <c r="I3">
-        <v>-0.07731694828469021</v>
+        <v>-0.1463990554899646</v>
       </c>
       <c r="J3">
-        <v>-0.07731694828469021</v>
+        <v>-0.1463990554899646</v>
       </c>
       <c r="K3">
-        <v>-44.4</v>
+        <v>-111.3</v>
       </c>
       <c r="L3">
-        <v>-0.2273425499231951</v>
+        <v>-0.6570247933884297</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>18.7</v>
+        <v>15.6</v>
       </c>
       <c r="V3">
-        <v>0.03883696780893042</v>
+        <v>0.05198267244251915</v>
       </c>
       <c r="W3">
-        <v>-0.1256366723259762</v>
+        <v>-0.3748736948467498</v>
       </c>
       <c r="X3">
-        <v>0.1965032588824319</v>
+        <v>0.1661181589380553</v>
       </c>
       <c r="Y3">
-        <v>-0.3221399312084081</v>
+        <v>-0.5409918537848051</v>
       </c>
       <c r="Z3">
-        <v>0.4596375617792422</v>
+        <v>0.4574669187145557</v>
       </c>
       <c r="AA3">
-        <v>-0.03553777359378677</v>
+        <v>-0.06697272481771537</v>
       </c>
       <c r="AB3">
-        <v>0.1724582500740713</v>
+        <v>0.142196188216278</v>
       </c>
       <c r="AC3">
-        <v>-0.207996023667858</v>
+        <v>-0.2091689130339934</v>
       </c>
       <c r="AD3">
-        <v>92.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>92.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AG3">
-        <v>73.39999999999999</v>
+        <v>56.8</v>
       </c>
       <c r="AH3">
-        <v>0.1605648535564853</v>
+        <v>0.1943624161073826</v>
       </c>
       <c r="AI3">
-        <v>0.2367609254498715</v>
+        <v>0.24409979770735</v>
       </c>
       <c r="AJ3">
-        <v>0.1322760857812218</v>
+        <v>0.1591482207901373</v>
       </c>
       <c r="AK3">
-        <v>0.1982176613556576</v>
+        <v>0.202135231316726</v>
       </c>
       <c r="AL3">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="AM3">
-        <v>2.73</v>
+        <v>3.98</v>
       </c>
       <c r="AN3">
-        <v>45.59405940594059</v>
+        <v>41.13636363636364</v>
       </c>
       <c r="AO3">
-        <v>-5.531135531135531</v>
+        <v>-6.231155778894473</v>
       </c>
       <c r="AP3">
-        <v>36.33663366336634</v>
+        <v>32.27272727272727</v>
       </c>
       <c r="AQ3">
-        <v>-5.531135531135531</v>
+        <v>-6.231155778894473</v>
       </c>
     </row>
   </sheetData>
